--- a/artfynd/A 63535-2025 artfynd.xlsx
+++ b/artfynd/A 63535-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>88420234</v>
       </c>
       <c r="B2" t="n">
-        <v>87921</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496929.543957025</v>
+        <v>496930</v>
       </c>
       <c r="R2" t="n">
-        <v>6594043.731138826</v>
+        <v>6594044</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2020-10-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,50 +777,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88166628</v>
+        <v>96294353</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88867</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>1227</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kryddtofsskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pholiota squarrosoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Peck) Sacc.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen vid Lakärret, Vstm</t>
+          <t>Lakärret, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496995.7633685307</v>
+        <v>496960</v>
       </c>
       <c r="R3" t="n">
-        <v>6594133.583166384</v>
+        <v>6594057</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,22 +843,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,40 +869,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>fuktig blandskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Camilla Pettersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Camilla Pettersson, Anders Carlberg, Herbert Kaufmann, Owe Nilsson, Berit Ragné, Renate Schwencke</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88166629</v>
+        <v>96294314</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,34 +896,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>3295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Clavulinopsis helvola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen vid Lakärret, Vstm</t>
+          <t>Lakärret, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496993.184825248</v>
+        <v>496960</v>
       </c>
       <c r="R4" t="n">
-        <v>6594090.410572046</v>
+        <v>6594057</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,22 +951,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
+          <t>2021-09-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,24 +977,443 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>planterad granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Camilla Pettersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Camilla Pettersson, Anders Carlberg, Herbert Kaufmann, Owe Nilsson, Berit Ragné, Renate Schwencke</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96294311</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89081</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4374</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulvaxing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lakärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>496960</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6594057</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Camilla Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Camilla Pettersson, Anders Carlberg, Herbert Kaufmann, Owe Nilsson, Berit Ragné, Renate Schwencke</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96294271</v>
+      </c>
+      <c r="B6" t="n">
+        <v>89085</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Toppvaxing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lakärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>496960</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6594057</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Camilla Pettersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Camilla Pettersson, Anders Carlberg, Herbert Kaufmann, Owe Nilsson, Berit Ragné, Renate Schwencke</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88166628</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen vid Lakärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>496996</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6594134</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>fuktig blandskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>88166629</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen vid Lakärret, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496993</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6594090</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>planterad granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 63535-2025 artfynd.xlsx
+++ b/artfynd/A 63535-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88420234</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96294353</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96294314</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96294311</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96294271</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88166628</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,8 +1453,22 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88166629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>